--- a/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
+++ b/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45.7109375" customWidth="1" style="20" min="2" max="2"/>
@@ -797,6 +797,7 @@
     <col width="60" customWidth="1" style="20" min="16" max="16"/>
     <col width="60" customWidth="1" style="20" min="17" max="17"/>
     <col width="60" customWidth="1" style="20" min="18" max="18"/>
+    <col width="55" customWidth="1" style="20" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1" s="20">
@@ -895,6 +896,11 @@
       <c r="R2" s="23" t="inlineStr">
         <is>
           <t>Комментарий замера (доп. показатели, потоки)</t>
+        </is>
+      </c>
+      <c r="S2" s="23" t="inlineStr">
+        <is>
+          <t>Ключи замеров</t>
         </is>
       </c>
     </row>
@@ -997,6 +1003,11 @@
           <t>Не заполняется, пишется стандартный комментарий сеанса БСП. Потоки: при фоновом режиме проверку выполняют параллельные задания, число потоков обработки = параметр сеанса ПотоковНаСеансПроверкиЛимитов, чтения - 4/2/3/4 по видам.</t>
         </is>
       </c>
+      <c r="S4" s="24" t="inlineStr">
+        <is>
+          <t>Проверка и этапы ЧтениеПредварительное, ДействующиеЛимиты, ЧтениеНаборовДанныхЛимитов, ПорогиБазисыПростые, ОбработкаПроверки, ЗаписьРезультатов (существующие)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="180" customHeight="1" s="20">
       <c r="A5" t="n">
@@ -1061,12 +1072,12 @@
       </c>
       <c r="O5" s="24" t="inlineStr">
         <is>
-          <t>Расширение FO_KeyOpsPerf (отдельный ключ постконтроля)</t>
+          <t>Расширение FO_KeyOpsPerf</t>
         </is>
       </c>
       <c r="P5" s="24" t="inlineStr">
         <is>
-          <t>Сейчас пишется под тем же ключом "Проверка", что и предконтроль - разделить нельзя. Добавить внешний замер "ПостКонтроль" на всю процедуру (сбор портфелей + проверка + постановка в очередь рассылки)</t>
+          <t>Сейчас пишется под тем же ключом "Проверка", что и предконтроль - разделить нельзя. Добавляется внешний замер ПроверкаЛимитов.ПостКонтроль на всю процедуру (сбор портфелей + проверка + постановка в очередь рассылки); существующий замер "Проверка" остается</t>
         </is>
       </c>
       <c r="Q5" s="24" t="inlineStr">
@@ -1077,6 +1088,11 @@
       <c r="R5" s="24" t="inlineStr">
         <is>
           <t>Групп и портфелей в настройке: N; Фоновые задания: Да/Нет; Потоков проверки: K; Дата проверки: Д. K = параметр сеанса ПотоковНаСеансПроверкиЛимитов.</t>
+        </is>
+      </c>
+      <c r="S5" s="24" t="inlineStr">
+        <is>
+          <t>ПроверкаЛимитов.ПостКонтроль (новый); внутри по-прежнему пишется существующий Проверка</t>
         </is>
       </c>
     </row>
@@ -1141,6 +1157,11 @@
       <c r="R6" s="24" t="inlineStr">
         <is>
           <t>Класс: комплаенс/риски; Создано установок: N; Без эталона или с ошибкой: M. Выполняется в одном сеансе, последовательно по классам.</t>
+        </is>
+      </c>
+      <c r="S6" s="24" t="inlineStr">
+        <is>
+          <t>РаспространениеПравилЛимитов, .ПоискНовыхКлиентов, .СозданиеУстановок, .Рассылка</t>
         </is>
       </c>
     </row>
@@ -1231,6 +1252,11 @@
           <t>Не заполняется (стандартный комментарий сеанса БСП).</t>
         </is>
       </c>
+      <c r="S8" s="24" t="inlineStr">
+        <is>
+          <t>Отправка (существующий)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1297,6 +1323,11 @@
       <c r="R9" s="24" t="inlineStr">
         <is>
           <t>Поручений создано: N; Отправлено: M; Ошибок: E. Сама обработка однопоточная; проверка и отправка внутри идут через Распорядители с их потоками.</t>
+        </is>
+      </c>
+      <c r="S9" s="24" t="inlineStr">
+        <is>
+          <t>СозданиеТорговыхПорученийРОСТ.Покупка, СозданиеТорговыхПорученийРОСТ.Продажа; шаги .ОтборПортфелей, .СозданиеИОтправка, .Рассылка</t>
         </is>
       </c>
     </row>
@@ -1395,6 +1426,11 @@
           <t>Пакет: Портфелей: N; Строк: M; Разделов: K; Пакет: УИД. Раздел: Строк: N; Пакет: УИД (по УИД разделы связываются с пакетом). Для ДополнительныеСведения еще Записано: M - сколько строк записано после пропуска одинаковых флагов (IMDEV-9532). Потоки: МО грузит в 5 потоков, на стороне ФО число потоков не передается; параллельность считается по пересечению интервалов замеров разных сеансов (номер сеанса есть в каждой записи замера).</t>
         </is>
       </c>
+      <c r="S11" s="24" t="inlineStr">
+        <is>
+          <t>ОбменБэкОфис.Пакет, ОбменБэкОфис.РегистрыСведений.&lt;Имя&gt;, ОбменБэкОфис.ОперацииПослеОбмена</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1469,6 +1505,11 @@
           <t>Строк: N; Пакет: УИД. Потоки: как в строке 6.</t>
         </is>
       </c>
+      <c r="S12" s="24" t="inlineStr">
+        <is>
+          <t>ОбменБэкОфис.Справочники.&lt;Имя&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="90" customHeight="1" s="20">
       <c r="A13" t="n">
@@ -1543,6 +1584,11 @@
           <t>Строк: N; Пакет: УИД. Потоки: как в строке 6.</t>
         </is>
       </c>
+      <c r="S13" s="24" t="inlineStr">
+        <is>
+          <t>ОбменБэкОфис.Документы.&lt;Имя&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="60" customHeight="1" s="20">
       <c r="A14" t="n">
@@ -1617,6 +1663,11 @@
           <t>Депозитов ДУ/ПИФ/Calipso: a/b/c; Обновлено: N; Не найдено: M. Количество депозитов, которое просит постановка, - в комментарии. Однопоточно.</t>
         </is>
       </c>
+      <c r="S14" s="24" t="inlineStr">
+        <is>
+          <t>ЗагрузкаДепозитов, .ЗаполнитьДепозиты, .ОбновитьФактическуюПозицию, .Рассылка</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1" s="20">
       <c r="A15" t="n">
@@ -1691,6 +1742,11 @@
           <t>Активов: N; Дата котировок: Д. Однопоточно.</t>
         </is>
       </c>
+      <c r="S15" s="24" t="inlineStr">
+        <is>
+          <t>ЗагрузкаКотировокММВБ, .Чтение, .Запись</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="60" customHeight="1" s="20">
       <c r="A16" t="n">
@@ -1765,6 +1821,11 @@
           <t>Индексов: N; Записей состава: M; Источник: MICROAPI/TIBCO. Однопоточно.</t>
         </is>
       </c>
+      <c r="S16" s="24" t="inlineStr">
+        <is>
+          <t>ЗагрузкаИндексов, .Чтение, .Запись</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="60" customHeight="1" s="20">
       <c r="A17" t="n">
@@ -1837,6 +1898,11 @@
           <t>Строк из Rates: N; Сопоставлено: M. Однопоточно.</t>
         </is>
       </c>
+      <c r="S17" s="24" t="inlineStr">
+        <is>
+          <t>ЗагрузкаTCRIS, .ЧтениеRates, .Сопоставление, .Запись</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="60" customHeight="1" s="20">
       <c r="A18" t="n">
@@ -1909,6 +1975,11 @@
       <c r="R18" s="24" t="inlineStr">
         <is>
           <t>Поручений создано: N; Портфелей: 0 при холостом запуске. Однопоточно; проверка и отправка - через Распорядители.</t>
+        </is>
+      </c>
+      <c r="S18" s="24" t="inlineStr">
+        <is>
+          <t>ЗагрузкаНеторговыхПорученийРОСТ, .СозданиеПоручений, .Рассылка</t>
         </is>
       </c>
     </row>
@@ -2000,6 +2071,11 @@
           <t>Сделок: N. Однопоточно.</t>
         </is>
       </c>
+      <c r="S20" s="24" t="inlineStr">
+        <is>
+          <t>ИсполнениеСделок, .ЗаполнитьТаблицуСделок, .Проведение</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20.25" customHeight="1" s="20">
       <c r="A21" t="n">
@@ -2051,6 +2127,11 @@
       <c r="R21" s="24" t="inlineStr">
         <is>
           <t>Не заполняется (стандартный комментарий сеанса БСП).</t>
+        </is>
+      </c>
+      <c r="S21" s="24" t="inlineStr">
+        <is>
+          <t>ОбработатьПакет (существующий)</t>
         </is>
       </c>
     </row>
@@ -2127,6 +2208,11 @@
           <t>Активных торговых дат: N. Однопоточно.</t>
         </is>
       </c>
+      <c r="S23" s="24" t="inlineStr">
+        <is>
+          <t>УпаковкаДанных, .КэшВмОписания, .ОчиститьСлужебныеКэши, .ОчиститьДанныеНеактивныхСеансов, .Сократить.&lt;Регистр&gt;</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
+++ b/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
@@ -1408,12 +1408,12 @@
       </c>
       <c r="O11" s="24" t="inlineStr">
         <is>
-          <t>Расширение FO_KeyOpsPerf; регистр ДополнительныеСведения - копия расширения FO_PositionLoadOpt (IMDEV-9532)</t>
+          <t>Расширение FO_KeyOpsPerf; регистр ДополнительныеСведения - выполнено в задаче IMDEV-9532 (FO_PositionLoadOpt 1.0.0.5)</t>
         </is>
       </c>
       <c r="P11" s="24" t="inlineStr">
         <is>
-          <t>Одна запись на вид регистра за пакет, вокруг вызова в диспетчере ОбработатьДанные_РегистрыСведений, только для непустого раздела; плюс весь пакет ЗагрузитьПакет и шаг ВыполнитьОперацииПослеОбмена. Регистр ДополнительныеСведения замеряется внутри перехвата ОбработатьДанные_ДополнительныеСведения в копии расширения IMDEV-9532, в диспетчере его нет. Сжатый пакет (DownloadCompressedPosition) идет в тот же ЗагрузитьПакет</t>
+          <t>Одна запись на вид регистра за пакет, вокруг вызова в диспетчере ОбработатьДанные_РегистрыСведений, только для непустого раздела; плюс весь пакет ЗагрузитьПакет и шаг ВыполнитьОперацииПослеОбмена. Замер регистра ДополнительныеСведения выполнен в задаче IMDEV-9532 (внутри перехвата ОбработатьДанные_ДополнительныеСведения, FO_PositionLoadOpt 1.0.0.5), в диспетчере его нет. Сжатый пакет (DownloadCompressedPosition) идет в тот же ЗагрузитьПакет</t>
         </is>
       </c>
       <c r="Q11" s="24" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="R11" s="24" t="inlineStr">
         <is>
-          <t>Пакет: Портфелей: N; Строк: M; Разделов: K; Пакет: УИД. Раздел: Строк: N; Пакет: УИД (по УИД разделы связываются с пакетом). Для ДополнительныеСведения еще Записано: M - сколько строк записано после пропуска одинаковых флагов (IMDEV-9532). Потоки: МО грузит в 5 потоков, на стороне ФО число потоков не передается; параллельность считается по пересечению интервалов замеров разных сеансов (номер сеанса есть в каждой записи замера).</t>
+          <t>Пакет: Портфелей: N; Строк: M; Разделов: K; Пакет: УИД. Раздел: Строк: N; Пакет: УИД (по УИД разделы связываются с пакетом). Замер ДополнительныеСведения (с полем Записано: M - сколько строк записано после пропуска одинаковых флагов) выполнен в задаче IMDEV-9532, расширение FO_PositionLoadOpt 1.0.0.5. Потоки: МО грузит в 5 потоков, на стороне ФО число потоков не передается; параллельность считается по пересечению интервалов замеров разных сеансов (номер сеанса есть в каждой записи замера).</t>
         </is>
       </c>
       <c r="S11" s="24" t="inlineStr">

--- a/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
+++ b/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Q5" s="24" t="inlineStr">
         <is>
-          <t>Портфели проверки: число портфелей после раскрытия групп и исключения неактивных.</t>
+          <t>Портфели проверки: число портфелей после раскрытия групп и исключения неактивных; если портфелей нет - 1.</t>
         </is>
       </c>
       <c r="R5" s="24" t="inlineStr">
         <is>
-          <t>Групп и портфелей в настройке: N; Фоновые задания: Да/Нет; Потоков проверки: K; Дата проверки: Д. K = параметр сеанса ПотоковНаСеансПроверкиЛимитов.</t>
+          <t>Групп и портфелей в настройке: N; Портфелей: M; Фоновые задания: Да/Нет; Потоков проверки: K; Дата проверки: Д. K = параметр сеанса ПотоковНаСеансПроверкиЛимитов. Замер на всю процедуру, включая постановку ведомостей в очередь рассылки (при заданной настройке рассылки писем штатный код делает там паузу 10 секунд). Пишется и при досрочном завершении: нет портфелей в настройке (признак ошибки) или все портфели неактивны - тогда вместо потоков Проверка не выполнялась. Отказ проверки - признак ошибки замера.</t>
         </is>
       </c>
       <c r="S5" s="24" t="inlineStr">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="Q12" s="24" t="inlineStr">
         <is>
-          <t>Раздел Портфели: число элементов (каждый элемент - договор). Субпортфели, МестаХранения, МодельныеПортфели: число разных портфелей. Остальные справочники: число элементов.</t>
+          <t>Раздел Портфели: число элементов (каждый элемент - договор). Субпортфели, МестаХранения, МодельныеПортфели: число разных портфелей. АффилированныеЛица (второй проход по разделу Контрагенты): число контрагентов с аффилированными лицами, без них замер не пишется. Остальные справочники: число элементов.</t>
         </is>
       </c>
       <c r="R12" s="24" t="inlineStr">
         <is>
-          <t>Строк: N; Пакет: УИД. Потоки: как в строке 6.</t>
+          <t>Строк: N; Портфелей: M; Пакет: УИД; для АффилированныеЛица еще Аффилированных лиц: K. Потоки: как в строке 6.</t>
         </is>
       </c>
       <c r="S12" s="24" t="inlineStr">
         <is>
-          <t>ОбменБэкОфис.Справочники.&lt;Имя&gt;</t>
+          <t>ОбменБэкОфис.Справочники.&lt;Имя&gt;, &lt;Имя&gt; - имя раздела пакета XDTO (например ТипыКлиентов, Контрагенты), второй проход по контрагентам - АффилированныеЛица</t>
         </is>
       </c>
     </row>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="Q13" s="24" t="inlineStr">
         <is>
-          <t>Документы с портфелем (СделкаРЕПО, ИсполненияПоСделке, РегистрацияПлановойПозиции и др.): число разных портфелей. КотировкиЦБНаБирже и прочие без портфеля: число документов.</t>
+          <t>Документы с портфелем (СделкаСЦеннымиБумагами, СделкаРЕПО, ИсполненияПоСделке, РегистрацияПлановойПозиции и др.): число разных портфелей. КотировкиЦБНаБирже: число котировок (один документ содержит котировки всех бумаг на дату). Прочие без портфеля: число документов.</t>
         </is>
       </c>
       <c r="R13" s="24" t="inlineStr">
         <is>
-          <t>Строк: N; Пакет: УИД. Потоки: как в строке 6.</t>
+          <t>Строк: N; Портфелей: M; Пакет: УИД; для котировок еще Котировок: K. Потоки: как в строке 6.</t>
         </is>
       </c>
       <c r="S13" s="24" t="inlineStr">
         <is>
-          <t>ОбменБэкОфис.Документы.&lt;Имя&gt;</t>
+          <t>ОбменБэкОфис.Документы.&lt;Имя&gt;, &lt;Имя&gt; - имя раздела пакета XDTO (например КотировкиЦБНаБирже, СделкаСЦеннымиБумагами)</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Q20" s="24" t="inlineStr">
         <is>
-          <t>Разные портфели в таблице сделок к исполнению.</t>
+          <t>Разные портфели в таблице сделок к исполнению; если портфелей нет - число строк, если и строк нет - 1.</t>
         </is>
       </c>
       <c r="R20" s="24" t="inlineStr">
         <is>
-          <t>Сделок: N. Однопоточно.</t>
+          <t>Строк: N; Сделок: D; Портфелей: M; Запуск: регламентное задание/вручную. Строка таблицы - остаток плановой позиции по сделке (бумага или деньги), на каждую строку создается документ исполнения. Однопоточно.</t>
         </is>
       </c>
       <c r="S20" s="24" t="inlineStr">

--- a/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
+++ b/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P11" s="24" t="inlineStr">
         <is>
-          <t>Одна запись на вид регистра за пакет, вокруг вызова в диспетчере ОбработатьДанные_РегистрыСведений, только для непустого раздела; плюс весь пакет ЗагрузитьПакет и шаг ВыполнитьОперацииПослеОбмена. Замер регистра ДополнительныеСведения выполнен в задаче IMDEV-9532 (внутри перехвата ОбработатьДанные_ДополнительныеСведения, FO_PositionLoadOpt 1.0.0.5), в диспетчере его нет. Сжатый пакет (DownloadCompressedPosition) идет в тот же ЗагрузитьПакет</t>
+          <t>Одна запись на вид регистра за пакет, вокруг вызова в диспетчере ОбработатьДанные_РегистрыСведений, только для непустого раздела; плюс весь пакет ЗагрузитьПакет; длительность ВыполнитьОперацииПослеОбмена - полем комментария пакета, без отдельной записи. Замер регистра ДополнительныеСведения выполнен в задаче IMDEV-9532 (внутри перехвата ОбработатьДанные_ДополнительныеСведения, FO_PositionLoadOpt 1.0.0.5), в диспетчере его нет. Сжатый пакет (DownloadCompressedPosition) идет в тот же ЗагрузитьПакет</t>
         </is>
       </c>
       <c r="Q11" s="24" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="R11" s="24" t="inlineStr">
         <is>
-          <t>Пакет: Портфелей: N; Строк: M; Разделов: K; Пакет: УИД. Раздел: Строк: N; Пакет: УИД (по УИД разделы связываются с пакетом). Замер ДополнительныеСведения (с полем Записано: M - сколько строк записано после пропуска одинаковых флагов) выполнен в задаче IMDEV-9532, расширение FO_PositionLoadOpt 1.0.0.5. Потоки: МО грузит в 5 потоков, на стороне ФО число потоков не передается; параллельность считается по пересечению интервалов замеров разных сеансов (номер сеанса есть в каждой записи замера).</t>
+          <t>Пакет: Портфелей: N; Строк: M; Разделов: K; Код ответа: C; Операции после обмена: T с; Пакет: УИД (поле операций - если задана константа "Операции после обмена"; отдельной записи нет). Раздел: Строк: N; Пакет: УИД (по УИД разделы связываются с пакетом). Замер ДополнительныеСведения (с полем Записано: M - сколько строк записано после пропуска одинаковых флагов) выполнен в задаче IMDEV-9532, расширение FO_PositionLoadOpt 1.0.0.5. Потоки: МО грузит в 5 потоков, на стороне ФО число потоков не передается; параллельность считается по пересечению интервалов замеров разных сеансов (номер сеанса есть в каждой записи замера).</t>
         </is>
       </c>
       <c r="S11" s="24" t="inlineStr">
         <is>
-          <t>ОбменБэкОфис.Пакет, ОбменБэкОфис.РегистрыСведений.&lt;Имя&gt;, ОбменБэкОфис.ОперацииПослеОбмена</t>
+          <t>ОбменБэкОфис.Пакет, ОбменБэкОфис.РегистрыСведений.&lt;Имя&gt;</t>
         </is>
       </c>
     </row>

--- a/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
+++ b/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
@@ -1136,7 +1136,7 @@
       <c r="M6" s="9" t="n"/>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>Внешняя обработка "Распространение правил с одного клиента на список клиентов" (внРаспространениеПравилСОдногоКлиентаНаСписокКлиентов, версия 1.14), метод ВыполнитьРаспространениеПравилПослеОбмена; вызывается из обработки "Операции после обмена" после загрузки из МО</t>
+          <t>Внешняя обработка "Распространение правил с одного клиента на список клиентов" (внРаспространениеПравилСОдногоКлиентаНаСписокКлиентов, версия 1.15), метод ВыполнитьРаспространениеПравилПослеОбмена; вызывается из обработки "Операции после обмена" после загрузки из МО</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -1312,22 +1312,22 @@
       </c>
       <c r="P9" s="24" t="inlineStr">
         <is>
-          <t>Отдельные ключи для покупки и продажи; шаги: отбор портфелей, создание и отправка поручений, рассылка отчета. Вызовы Распорядители внутри уже замеряются</t>
+          <t>Отдельные ключи для покупки и продажи, замер длительной операции БСП. Шаги по местам будущей оптимизации (IMDEV-9531): отбор портфелей, расчет потоков ОФЗ, запись и первое проведение поручения, цена из стакана, проведения с ценой, суммой и количеством, статус портфеля, проверка и отправка, рассылка; время шагов суммируется по поручениям прогона. Вызовы Распорядители внутри уже замеряются</t>
         </is>
       </c>
       <c r="Q9" s="24" t="inlineStr">
         <is>
-          <t>Портфели: строки списка портфелей на покупку; для продажи - число разных портфелей в списке продажи.</t>
+          <t>Шаг: число единиц шага - портфели отбора, ОФЗ в настройке стратегий, поручения (шаги записи, цены, проведений и статуса суммируются по всем поручениям прогона), отправленные поручения, 1 для рассылки; время записи шага - среднее на единицу (правило БСП для длительных операций), полное время шага = время x вес. Общая запись ветки - время всей ветки, вес - сумма весов шагов (правило БСП).</t>
         </is>
       </c>
       <c r="R9" s="24" t="inlineStr">
         <is>
-          <t>Поручений создано: N; Отправлено: M; Ошибок: E. Сама обработка однопоточная; проверка и отправка внутри идут через Распорядители с их потоками.</t>
+          <t>Общая запись: Портфелей: N; Поручений создано: M; Отправлено: K; Ошибок: E; Проведений: P (P - все проведения поручений за прогон, показывает число проведений на поручение). Шаги - без комментария. Около 10 записей на прогон при любом числе поручений. Шаги выбраны под оптимизацию IMDEV-9531: пакетный запрос цены из стакана, сокращение 2-4 проведений поручения, вынос запроса цены из транзакции, индекс в запросе отбора продажи.</t>
         </is>
       </c>
       <c r="S9" s="24" t="inlineStr">
         <is>
-          <t>СозданиеТорговыхПорученийРОСТ.Покупка, СозданиеТорговыхПорученийРОСТ.Продажа; шаги .ОтборПортфелей, .СозданиеИОтправка, .Рассылка</t>
+          <t>СозданиеТорговыхПорученийРОСТ.Покупка, СозданиеТорговыхПорученийРОСТ.Продажа - длительная операция БСП; шаги .ОтборПортфелей, .РасчетПотоковОФЗ (покупка), .ЗаписьПоручения, .ЦенаИзСтакана, .ПроведениеСЦеной, .ПроведениеСуммы, .ПроведениеКоличества (покупка ОФЗ), .СтатусПортфеля, .ПроверкаИОтправка, .Рассылка; итог .Удельный</t>
         </is>
       </c>
     </row>

--- a/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
+++ b/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
@@ -1151,12 +1151,12 @@
       </c>
       <c r="Q6" s="24" t="inlineStr">
         <is>
-          <t>Портфели новых клиентов, найденные для распространения правил (по каждому классу лимитов).</t>
+          <t>Общая запись: портфели, на которые распространены правила за прогон (не меньше 1). Шаги по каждому классу лимитов: поиск - найденные новые клиенты, создание установок - портфели с распространением, рассылка - 1 (пишется только при отправке письма).</t>
         </is>
       </c>
       <c r="R6" s="24" t="inlineStr">
         <is>
-          <t>Класс: комплаенс/риски; Создано установок: N; Без эталона или с ошибкой: M. Выполняется в одном сеансе, последовательно по классам.</t>
+          <t>Шаги: Класс: комплаенс/риски; Новых клиентов: N; Распространено: M; Уже с установкой: U; Без автоустановки: E. Общая запись: Классов: K; Новых клиентов: N; Распространено: M; Без автоустановки: E; Запись версий лимитов в фоне: P (P - пары портфель и класс, переданные фоновому заданию записи версий; только розничный ДУ). Фоновое задание записи версий лимитов (версия 1.15) выполняется после процедуры и в замер не входит.</t>
         </is>
       </c>
       <c r="S6" s="24" t="inlineStr">
@@ -1302,7 +1302,7 @@
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="24" t="inlineStr">
         <is>
-          <t>Внешняя обработка внСозданиеТорговыхПорученийРОСТ (версия 1.15), ВыполнитьКоманду: ФоновоеВыполнениеПокупка / ФоновоеВыполнениеПродажа</t>
+          <t>Внешняя обработка внСозданиеТорговыхПорученийРОСТ (версия 1.15): команды ФоновоеВыполнениеПокупка / ФоновоеВыполнениеПродажа, вызовы формы (покупка, продажа, реинвестирование, отправка пачки), фоновые потоки реинвестирования и продаж под блокировки</t>
         </is>
       </c>
       <c r="O9" s="24" t="inlineStr">
@@ -1312,22 +1312,22 @@
       </c>
       <c r="P9" s="24" t="inlineStr">
         <is>
-          <t>Отдельные ключи для покупки и продажи, замер длительной операции БСП. Шаги по местам будущей оптимизации (IMDEV-9531): отбор портфелей, расчет потоков ОФЗ, запись и первое проведение поручения, цена из стакана, проведения с ценой, суммой и количеством, статус портфеля, проверка и отправка, рассылка; время шагов суммируется по поручениям прогона. Вызовы Распорядители внутри уже замеряются</t>
+          <t>Отдельные ключи для покупки, продажи, реинвестирования, продаж под блокировки и отправки пачки; замер длительной операции БСП, каждая точка входа (команда, форма, поток) начинает его сама. Шаги по местам будущей оптимизации (IMDEV-9531): отбор портфелей, расчет потоков и количества ОФЗ, запись и первое проведение поручения, цена из стакана, цена закрытия, проведения с ценой, суммой и количеством, статус портфеля, проверка и отправка, рассылка; время шагов суммируется по поручениям. Вызовы Распорядители внутри уже замеряются</t>
         </is>
       </c>
       <c r="Q9" s="24" t="inlineStr">
         <is>
-          <t>Шаг: число единиц шага - портфели отбора, ОФЗ в настройке стратегий, поручения (шаги записи, цены, проведений и статуса суммируются по всем поручениям прогона), отправленные поручения, 1 для рассылки; время записи шага - среднее на единицу (правило БСП для длительных операций), полное время шага = время x вес. Общая запись ветки - время всей ветки, вес - сумма весов шагов (правило БСП).</t>
+          <t>Шаг: число единиц шага - строки отбора, ОФЗ в настройке стратегий, поручения (шаги записи, цены, проведений и статуса суммируются по всем поручениям прогона), отправленные поручения, 1 для рассылки и завершения; время записи шага - среднее на единицу (правило БСП для длительных операций), полное время шага = время x вес. Общая запись - полное время операции, вес - сумма весов шагов (правило БСП).</t>
         </is>
       </c>
       <c r="R9" s="24" t="inlineStr">
         <is>
-          <t>Общая запись: Портфелей: N; Поручений создано: M; Отправлено: K; Ошибок: E; Проведений: P (P - все проведения поручений за прогон, показывает число проведений на поручение). Шаги - без комментария. Около 10 записей на прогон при любом числе поручений. Шаги выбраны под оптимизацию IMDEV-9531: пакетный запрос цены из стакана, сокращение 2-4 проведений поручения, вынос запроса цены из транзакции, индекс в запросе отбора продажи.</t>
+          <t>Общая запись: Запуск: регламентное задание | форма | поток N; Портфелей: K; Поручений: M; Проведений: P, у потоков еще Портфелей в пакете: B - фактическое число портфелей, распределенных по потокам в одном нажатии кнопки (по нему видно число запусков за день). Портфелей - строки списка операции или портфели потока. P - сумма весов шагов записи и перепроведения поручения. Потоки пакета пишут по записи на поток; сумма времени потоков больше длительности пакета (потоки работают параллельно): пакет целиком - от начала первого потока до конца записи .ОтправкаПачки. Шаги выбраны под оптимизацию IMDEV-9531: сокращение проведений поручения, индекс в запросе отбора продажи; шаг ЦенаИзСтакана показывает долю запроса цены внутри транзакции по портфелю.</t>
         </is>
       </c>
       <c r="S9" s="24" t="inlineStr">
         <is>
-          <t>СозданиеТорговыхПорученийРОСТ.Покупка, СозданиеТорговыхПорученийРОСТ.Продажа - длительная операция БСП; шаги .ОтборПортфелей, .РасчетПотоковОФЗ (покупка), .ЗаписьПоручения, .ЦенаИзСтакана, .ПроведениеСЦеной, .ПроведениеСуммы, .ПроведениеКоличества (покупка ОФЗ), .СтатусПортфеля, .ПроверкаИОтправка, .Рассылка; итог .Удельный</t>
+          <t>СозданиеТорговыхПорученийРОСТ.Покупка, .Продажа (команды регламентного задания и вызов из формы), .Реинвестирование (кнопка формы и каждый фоновый поток), .ПродажаПодБлокировки (каждый фоновый поток), .ОтправкаПачки (отправка поручений пакета из формы) - длительная операция БСП; шаги .ОтборПортфелей (команды), .РасчетПотоковОФЗ, .РасчетКоличестваОФЗ, .ПроведениеКоличества (покупка ОФЗ), .ЗаписьПоручения, .ЦенаИзСтакана, .ЦенаЗакрытия (при контроле по цене закрытия), .ПроведениеСЦеной, .ПроведениеСуммы, .СтатусПортфеля, .ПроверкаИОтправка, .Рассылка (команды) или .Завершение (форма и потоки); итог .Удельный</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Q18" s="24" t="inlineStr">
         <is>
-          <t>Портфели, отобранные для создания неторговых поручений. При нуле - вес 1.</t>
+          <t>Созданные поручения (каждое - один портфель); при нуле - вес 1 (решение В6).</t>
         </is>
       </c>
       <c r="R18" s="24" t="inlineStr">
         <is>
-          <t>Поручений создано: N; Портфелей: 0 при холостом запуске. Однопоточно; проверка и отправка - через Распорядители.</t>
+          <t>Поручений создано: N. Общая запись при исключении или ошибках создания поручений (важность ошибки 2) - с признаком "Выполнен с ошибкой". Нерабочий день по календарю биржи - выход до замера, записи нет.</t>
         </is>
       </c>
       <c r="S18" s="24" t="inlineStr">

--- a/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
+++ b/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
@@ -1640,7 +1640,7 @@
       <c r="M14" s="9" t="n"/>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>Внешняя обработка "Загрузка депозитов из внешних источников" (внЗагрузкаДепозитовИзВнешнихИсточников, версия 1.18 - подтверждено, что она на PROD), ВыполнитьКоманду "ФоновоеВыполнение"</t>
+          <t>Внешняя обработка "Загрузка депозитов из внешних источников" (внЗагрузкаДепозитовИзВнешнихИсточников, версия 1.18 -&gt; 1.19 - 1.18 подтверждена на PROD), ВыполнитьКоманду "ФоновоеВыполнение"</t>
         </is>
       </c>
       <c r="O14" s="24" t="inlineStr">
@@ -1650,17 +1650,17 @@
       </c>
       <c r="P14" s="24" t="inlineStr">
         <is>
-          <t>Шаги: ЗаполнитьДепозиты, ОбновитьФактическуюПозицию, рассылка</t>
+          <t>Шаги: ЗаполнитьДепозиты (получение из ДУ, ПИФ, Calipso и сопоставление), ОбновитьФактическуюПозицию (запись позиции и ставок, удаление закрытых, постановка пересчета РСА в фон - сам пересчет в замер не входит), рассылка. Замеры шагов внутри процедур, пишутся и при вызове с формы; кнопки формы, в том числе частичные загрузки, отдельно не замеряются. При сбое замер не пишется</t>
         </is>
       </c>
       <c r="Q14" s="24" t="inlineStr">
         <is>
-          <t>Портфели, по которым обновлена фактическая позиция депозитами.</t>
+          <t>Общая запись и шаг .ОбновитьФактическуюПозицию: портфели, по которым обновлена фактическая позиция депозитами (решение В8). Шаг .ЗаполнитьДепозиты: полученные депозиты (портфель известен только после сопоставления). .Рассылка: 1, пишется только при отправке письма.</t>
         </is>
       </c>
       <c r="R14" s="24" t="inlineStr">
         <is>
-          <t>Депозитов ДУ/ПИФ/Calipso: a/b/c; Обновлено: N; Не найдено: M. Количество депозитов, которое просит постановка, - в комментарии. Однопоточно.</t>
+          <t>Общая запись: Депозитов ДУ/ПИФ/Calipso: a/b/c; Обновлено: N; Не найдено: M - количество депозитов, которое просит постановка. .ЗаполнитьДепозиты: Депозитов ДУ/ПИФ/Calipso: a/b/c; .ОбновитьФактическуюПозицию: Обновлено: N; Не найдено: M. Пересчет фактической позиции и РСА выполняет фоновое задание другой обработки, в замер он не входит. При сбое замер не пишется (решение В8). Однопоточно.</t>
         </is>
       </c>
       <c r="S14" s="24" t="inlineStr">
@@ -1719,7 +1719,7 @@
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>Внешняя обработка внЗагрузкаКотировокММВБ (версия 1.02), ВыполнитьКоманду "ФоновоеВыполнение"</t>
+          <t>Внешняя обработка внЗагрузкаКотировокММВБ (версия 1.02 -&gt; 1.03), ВыполнитьКоманду "ФоновоеВыполнение"</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="P15" s="24" t="inlineStr">
         <is>
-          <t>Шаги: ЗагрузитьОбъекты (чтение из сервиса), СоздатьОбъекты (запись). Регламентное задание конфигурации АванкорЗагрузитьКотировкиММВБ отключено - не оно</t>
+          <t>Шаги: ЗагрузитьОбъекты (чтение из сервиса TIBCO, поиск активов), СоздатьОбъекты (документы котировок по бирже и дате, проведение). При сбое замер не пишется. Регламентное задание конфигурации АванкорЗагрузитьКотировкиММВБ отключено - не оно</t>
         </is>
       </c>
       <c r="Q15" s="24" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="R15" s="24" t="inlineStr">
         <is>
-          <t>Активов: N; Дата котировок: Д. Однопоточно.</t>
+          <t>Активов: N; Документов: D; Период: Д1 - Д2 (загрузка идет за интервал дат). При сбое замер не пишется (решение В8). Сбой - исключение или признак ошибки обработки, в том числе непроведенный документ котировок. Однопоточно.</t>
         </is>
       </c>
       <c r="S15" s="24" t="inlineStr">
@@ -1798,7 +1798,7 @@
       <c r="M16" s="9" t="n"/>
       <c r="N16" s="24" t="inlineStr">
         <is>
-          <t>Внешняя обработка внЗагрузкаИндексовФО (версия 1.03), ВыполнитьКоманду "ФоновоеВыполнение"</t>
+          <t>Внешняя обработка внЗагрузкаИндексовФО (версия 1.03 -&gt; 1.04), ВыполнитьКоманду "ФоновоеВыполнение"</t>
         </is>
       </c>
       <c r="O16" s="24" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
-          <t>Шаги: ЗагрузитьОбъекты (чтение), СоздатьОбъекты (запись). Индексы грузит только эта обработка (задание "Запуск дополнительных обработок", команда "Загрузить индексы (в фоне)", включено). Регламентное задание конфигурации "Загрузить индексы (ММВБ)" выключено - замер в нем не нужен</t>
+          <t>Шаги: ЗагрузитьОбъекты (чтение из MICROAPI или TIBCO), СоздатьОбъекты (данные и составы индексов). При сбое замер не пишется. Индексы грузит только эта обработка (задание "Запуск дополнительных обработок", команда "Загрузить индексы (в фоне)", включено). Регламентное задание конфигурации "Загрузить индексы (ММВБ)" выключено - замер в нем не нужен</t>
         </is>
       </c>
       <c r="Q16" s="24" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="R16" s="24" t="inlineStr">
         <is>
-          <t>Индексов: N; Записей состава: M; Источник: MICROAPI/TIBCO. Однопоточно.</t>
+          <t>Индексов: N; Записей состава: M; Источник: MICROAPI/TIBCO. При сбое замер не пишется (решение В8). Предупреждения загрузки сбоем не считаются. Однопоточно.</t>
         </is>
       </c>
       <c r="S16" s="24" t="inlineStr">
@@ -1875,7 +1875,7 @@
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="24" t="inlineStr">
         <is>
-          <t>Внешняя обработка "Загрузка доп реквизита TCRIS" (ЗагрузкаДопРеквизитаTCRIS, версия 1.01), ВыполнитьКоманду -&gt; ЗагрузитьTCRIS</t>
+          <t>Внешняя обработка "Загрузка доп реквизита TCRIS" (ЗагрузкаДопРеквизитаTCRIS, версия 1.01 -&gt; 1.02), ВыполнитьКоманду -&gt; ЗагрузитьTCRIS</t>
         </is>
       </c>
       <c r="O17" s="24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="P17" s="24" t="inlineStr">
         <is>
-          <t>Шаги: подключение и чтение из Rates, сопоставление контрагентов, запись значений</t>
+          <t>Шаги: подключение и чтение из базы Rates, сопоставление контрагентов по ИНН, запись сведения TCRIS. При сбое (в том числе Rates недоступна) замер не пишется. Адрес Rates задан в коде: на базе разработки проверяется ветка недоступности, загрузка с записью - на тестовой копии</t>
         </is>
       </c>
       <c r="Q17" s="24" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="R17" s="24" t="inlineStr">
         <is>
-          <t>Строк из Rates: N; Сопоставлено: M. Однопоточно.</t>
+          <t>Строк из Rates: N; Сопоставлено: M. При сбое замер не пишется (решение В8). Однопоточно.</t>
         </is>
       </c>
       <c r="S17" s="24" t="inlineStr">

--- a/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
+++ b/bases/Wim_Fo/projects/IMDEV-9530  Замеры ФО/Ключевые операции ФО_объекты замеров.xlsx
@@ -1660,7 +1660,7 @@
       </c>
       <c r="R14" s="24" t="inlineStr">
         <is>
-          <t>Общая запись: Депозитов ДУ/ПИФ/Calipso: a/b/c; Обновлено: N; Не найдено: M - количество депозитов, которое просит постановка. .ЗаполнитьДепозиты: Депозитов ДУ/ПИФ/Calipso: a/b/c; .ОбновитьФактическуюПозицию: Обновлено: N; Не найдено: M. Пересчет фактической позиции и РСА выполняет фоновое задание другой обработки, в замер он не входит. При сбое замер не пишется (решение В8). Однопоточно.</t>
+          <t>Общая запись: Депозитов ДУ/ПИФ/Calipso: a/b/c; Портфелей: P; Обновлено: N; Не найдено: M - количество депозитов, которое просит постановка. .ЗаполнитьДепозиты: Депозитов ДУ/ПИФ/Calipso: a/b/c; .ОбновитьФактическуюПозицию: Портфелей: P; Обновлено: N; Не найдено: M (не найдено - депозиты без места хранения или субпортфеля). Шаг обновления включает паузу 10 с перед постановкой рассылки по пересчету РСА; сам пересчет выполняет фоновое задание другой обработки, в замер он не входит. При сбое замер не пишется (решение В8): ни одного депозита ни из одного источника или ошибка отправки письма. Однопоточно.</t>
         </is>
       </c>
       <c r="S14" s="24" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="R15" s="24" t="inlineStr">
         <is>
-          <t>Активов: N; Документов: D; Период: Д1 - Д2 (загрузка идет за интервал дат). При сбое замер не пишется (решение В8). Сбой - исключение или признак ошибки обработки, в том числе непроведенный документ котировок. Однопоточно.</t>
+          <t>Общая запись: Котировок: N; Активов: M; Документов: D; Период: Д1 - Д2; .Чтение: Котировок: N; Активов: M; Период: Д1 - Д2; .Запись: Котировок: N; Активов: M; Документов: D (активов - котировки с найденной бумагой, документов - записанные документы котировок). При сбое замер не пишется (решение В8). Сбой - исключение или признак ошибки обработки, в том числе непроведенный документ котировок. Однопоточно.</t>
         </is>
       </c>
       <c r="S15" s="24" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="R16" s="24" t="inlineStr">
         <is>
-          <t>Индексов: N; Записей состава: M; Источник: MICROAPI/TIBCO. При сбое замер не пишется (решение В8). Предупреждения загрузки сбоем не считаются. Однопоточно.</t>
+          <t>Индексов: N; Записей: M; Записей состава: K; Источник: MICROAPI/TIBCO во всех записях (индексов - в запросе). При сбое замер не пишется (решение В8). Предупреждения загрузки сбоем не считаются. Однопоточно.</t>
         </is>
       </c>
       <c r="S16" s="24" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="R17" s="24" t="inlineStr">
         <is>
-          <t>Строк из Rates: N; Сопоставлено: M. При сбое замер не пишется (решение В8). Однопоточно.</t>
+          <t>Общая запись и .Запись: Строк из Rates: N; Сопоставлено: M; Контрагентов: K; .ЧтениеRates: Строк из Rates: N; .Сопоставление: Строк из Rates: N; Сопоставлено: M. При сбое (в том числе Rates недоступна) замер не пишется (решение В8). Однопоточно.</t>
         </is>
       </c>
       <c r="S17" s="24" t="inlineStr">
